--- a/results/exp_E_additional_metrics.xlsx
+++ b/results/exp_E_additional_metrics.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>File Index</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -441,27 +441,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Representation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Silhouette</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Davies-Bouldin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Calinski-Harabasz</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>WCSS</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Balance</t>
         </is>
       </c>
     </row>
@@ -471,23 +471,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DeepWalk kmeans</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.5612158179283142</v>
+          <t>BoW kmeans</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5955524666449151</v>
+        <v>0.09899495384260193</v>
       </c>
       <c r="E2" t="n">
-        <v>131.3990874121706</v>
+        <v>2.883163067215291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3925788253545761</v>
+        <v>8.281005595045158</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7872340425531915</v>
+        <v>285.1618625277162</v>
       </c>
     </row>
     <row r="3">
@@ -496,23 +498,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BoW kmeans</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.09899495384260193</v>
+          <t>BoW affinity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>2.883163067215291</v>
+        <v>0.1882577106825404</v>
       </c>
       <c r="E3" t="n">
-        <v>8.281005595045158</v>
+        <v>1.500462493096526</v>
       </c>
       <c r="F3" t="n">
-        <v>285.1618625277162</v>
+        <v>5.737850980611594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9024390243902439</v>
+        <v>149.3638655462185</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +525,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DeepWalk affinity</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.5382678508758545</v>
+          <t>BoW gmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4954908536947498</v>
+        <v>0.0811217904702006</v>
       </c>
       <c r="E4" t="n">
-        <v>296.836869691172</v>
+        <v>3.125084110983863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04858575644902885</v>
+        <v>6.986920167921451</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5873015873015873</v>
+        <v>289.8338235294117</v>
       </c>
     </row>
     <row r="5">
@@ -546,23 +552,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BoW affinity</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1882577106825404</v>
+          <t>BoW agglomerative</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>1.500462493096526</v>
+        <v>0.09045864377990695</v>
       </c>
       <c r="E5" t="n">
-        <v>5.737850980611594</v>
+        <v>3.077964836587991</v>
       </c>
       <c r="F5" t="n">
-        <v>149.3638655462185</v>
+        <v>7.338098863782334</v>
       </c>
       <c r="G5" t="n">
-        <v>0.334841628959276</v>
+        <v>288.5509157509157</v>
       </c>
     </row>
     <row r="6">
@@ -571,23 +579,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeepWalk gmm</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.4904718697071075</v>
+          <t>DeepWalk kmeans</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0.651770550146658</v>
+        <v>0.5862144827842712</v>
       </c>
       <c r="E6" t="n">
-        <v>105.7581717489198</v>
+        <v>0.5328837778025122</v>
       </c>
       <c r="F6" t="n">
-        <v>0.449206680059433</v>
+        <v>137.7623666627406</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.48897884786129</v>
       </c>
     </row>
     <row r="7">
@@ -596,23 +606,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BoW gmm</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0811217904702006</v>
+          <t>DeepWalk affinity</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>3.125084110983863</v>
+        <v>0.5653262138366699</v>
       </c>
       <c r="E7" t="n">
-        <v>6.986920167921451</v>
+        <v>0.428499515816736</v>
       </c>
       <c r="F7" t="n">
-        <v>289.8338235294117</v>
+        <v>316.5585425918941</v>
       </c>
       <c r="G7" t="n">
-        <v>0.925</v>
+        <v>0.05868154764175415</v>
       </c>
     </row>
     <row r="8">
@@ -621,23 +633,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DeepWalk agglomerative</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.485899955034256</v>
+          <t>DeepWalk gmm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6223464418113375</v>
+        <v>0.5850160717964172</v>
       </c>
       <c r="E8" t="n">
-        <v>95.13747310079293</v>
+        <v>0.5009565940322105</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4777514040470123</v>
+        <v>124.9096772030504</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.5208956003189087</v>
       </c>
     </row>
     <row r="9">
@@ -646,23 +660,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BoW agglomerative</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.09045864377990695</v>
+          <t>DeepWalk agglomerative</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>3.077964836587991</v>
+        <v>0.5862144827842712</v>
       </c>
       <c r="E9" t="n">
-        <v>7.338098863782334</v>
+        <v>0.5328837778025122</v>
       </c>
       <c r="F9" t="n">
-        <v>288.5509157509157</v>
+        <v>137.7623666627406</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.48897884786129</v>
       </c>
     </row>
     <row r="10">
@@ -671,23 +687,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DeepWalk kmeans</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.5667786002159119</v>
+          <t>BoW kmeans</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5997315290638092</v>
+        <v>0.2312577773387333</v>
       </c>
       <c r="E10" t="n">
-        <v>99.15635426633332</v>
+        <v>1.31258018263109</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3974940925836563</v>
+        <v>13.93082115703617</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9807692307692307</v>
+        <v>168.3068181818182</v>
       </c>
     </row>
     <row r="11">
@@ -696,23 +714,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BoW kmeans</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2312577773387333</v>
+          <t>BoW affinity</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>1.31258018263109</v>
+        <v>0.209266518243</v>
       </c>
       <c r="E11" t="n">
-        <v>13.93082115703617</v>
+        <v>1.648450125454293</v>
       </c>
       <c r="F11" t="n">
-        <v>168.3068181818182</v>
+        <v>7.700712665817981</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6375</v>
+        <v>105.4373737373737</v>
       </c>
     </row>
     <row r="12">
@@ -721,23 +741,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DeepWalk affinity</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.6375376582145691</v>
+          <t>BoW gmm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3806981518892444</v>
+        <v>0.2312577773387333</v>
       </c>
       <c r="E12" t="n">
-        <v>314.1875369217392</v>
+        <v>1.31258018263109</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03346901084296405</v>
+        <v>13.93082115703617</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5666666666666667</v>
+        <v>168.3068181818182</v>
       </c>
     </row>
     <row r="13">
@@ -746,23 +768,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BoW affinity</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.209266518243</v>
+          <t>BoW agglomerative</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>1.648450125454293</v>
+        <v>0.2312577773387333</v>
       </c>
       <c r="E13" t="n">
-        <v>7.700712665817981</v>
+        <v>1.31258018263109</v>
       </c>
       <c r="F13" t="n">
-        <v>105.4373737373737</v>
+        <v>13.93082115703617</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4857142857142857</v>
+        <v>168.3068181818182</v>
       </c>
     </row>
     <row r="14">
@@ -771,23 +795,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DeepWalk gmm</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.5667786002159119</v>
+          <t>DeepWalk kmeans</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5997315290638092</v>
+        <v>0.5674307942390442</v>
       </c>
       <c r="E14" t="n">
-        <v>99.15635426633332</v>
+        <v>0.566440271819975</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3974940925836563</v>
+        <v>92.70062338610398</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9807692307692307</v>
+        <v>0.3877125233411789</v>
       </c>
     </row>
     <row r="15">
@@ -796,23 +822,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BoW gmm</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.2312577773387333</v>
+          <t>DeepWalk affinity</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>1.31258018263109</v>
+        <v>0.5630049109458923</v>
       </c>
       <c r="E15" t="n">
-        <v>13.93082115703617</v>
+        <v>0.4266401207825184</v>
       </c>
       <c r="F15" t="n">
-        <v>168.3068181818182</v>
+        <v>235.5953261123342</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6375</v>
+        <v>0.04125531588215381</v>
       </c>
     </row>
     <row r="16">
@@ -821,23 +849,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DeepWalk agglomerative</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.5419988036155701</v>
+          <t>DeepWalk gmm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>0.509580594722585</v>
+        <v>0.5325750112533569</v>
       </c>
       <c r="E16" t="n">
-        <v>67.30189636511976</v>
+        <v>0.5360287452011125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5063657239079475</v>
+        <v>73.59466811289225</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6375</v>
+        <v>0.4481362700462341</v>
       </c>
     </row>
     <row r="17">
@@ -846,23 +876,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BoW agglomerative</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.2312577773387333</v>
+          <t>DeepWalk agglomerative</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>1.31258018263109</v>
+        <v>0.5727961659431458</v>
       </c>
       <c r="E17" t="n">
-        <v>13.93082115703617</v>
+        <v>0.5492530434097533</v>
       </c>
       <c r="F17" t="n">
-        <v>168.3068181818182</v>
+        <v>91.34367902571429</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6375</v>
+        <v>0.3914612233638763</v>
       </c>
     </row>
     <row r="18">
@@ -871,23 +903,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DeepWalk kmeans</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6614680290222168</v>
+          <t>BoW kmeans</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4317039380615699</v>
+        <v>0.1421446230393624</v>
       </c>
       <c r="E18" t="n">
-        <v>147.6490580697708</v>
+        <v>2.383358970820539</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2339422255754471</v>
+        <v>7.526422764227641</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7741935483870968</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="19">
@@ -896,23 +930,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BoW kmeans</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.1421446230393624</v>
+          <t>BoW affinity</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>2.383358970820539</v>
+        <v>0.1336567407551308</v>
       </c>
       <c r="E19" t="n">
-        <v>7.526422764227641</v>
+        <v>1.526538435264654</v>
       </c>
       <c r="F19" t="n">
-        <v>131.2</v>
+        <v>4.554556728768312</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8</v>
+        <v>84.95416666666668</v>
       </c>
     </row>
     <row r="20">
@@ -921,23 +957,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DeepWalk affinity</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.61222904920578</v>
+          <t>BoW gmm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>0.4351169536834705</v>
+        <v>0.1516341359345389</v>
       </c>
       <c r="E20" t="n">
-        <v>315.6793717677926</v>
+        <v>2.353287419659824</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02552666258998215</v>
+        <v>6.604677707901177</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5714285714285714</v>
+        <v>133.4989010989011</v>
       </c>
     </row>
     <row r="21">
@@ -946,23 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BoW affinity</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.1336567407551308</v>
+          <t>BoW agglomerative</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>1.526538435264654</v>
+        <v>0.1527805971388717</v>
       </c>
       <c r="E21" t="n">
-        <v>4.554556728768312</v>
+        <v>2.354060590087298</v>
       </c>
       <c r="F21" t="n">
-        <v>84.95416666666668</v>
+        <v>7.16784436083326</v>
       </c>
       <c r="G21" t="n">
-        <v>0.375</v>
+        <v>132.0848484848485</v>
       </c>
     </row>
     <row r="22">
@@ -971,23 +1011,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DeepWalk gmm</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.6614680290222168</v>
+          <t>DeepWalk kmeans</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>0.4317039380615699</v>
+        <v>0.5507810115814209</v>
       </c>
       <c r="E22" t="n">
-        <v>147.6490580697708</v>
+        <v>0.6371557872062439</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2339422255754471</v>
+        <v>81.03346512974771</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.4920984208583832</v>
       </c>
     </row>
     <row r="23">
@@ -996,23 +1038,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BoW gmm</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.1516341359345389</v>
+          <t>DeepWalk affinity</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>2.353287419659824</v>
+        <v>0.5502738356590271</v>
       </c>
       <c r="E23" t="n">
-        <v>6.604677707901177</v>
+        <v>0.4619557665516468</v>
       </c>
       <c r="F23" t="n">
-        <v>133.4989010989011</v>
+        <v>197.391764760306</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.07018777541816235</v>
       </c>
     </row>
     <row r="24">
@@ -1021,23 +1065,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DeepWalk agglomerative</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.6614680290222168</v>
+          <t>DeepWalk gmm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4317039380615699</v>
+        <v>0.5061162114143372</v>
       </c>
       <c r="E24" t="n">
-        <v>147.6490580697708</v>
+        <v>0.7678587945449742</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2339422255754471</v>
+        <v>47.68930326574657</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.6672368943691254</v>
       </c>
     </row>
     <row r="25">
@@ -1046,23 +1092,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BoW agglomerative</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.1527805971388717</v>
+          <t>DeepWalk agglomerative</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D25" t="n">
-        <v>2.354060590087298</v>
+        <v>0.5937971472740173</v>
       </c>
       <c r="E25" t="n">
-        <v>7.16784436083326</v>
+        <v>0.4014520883284426</v>
       </c>
       <c r="F25" t="n">
-        <v>132.0848484848485</v>
+        <v>52.60309681982113</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6339858453720808</v>
       </c>
     </row>
     <row r="26">
@@ -1071,23 +1119,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DeepWalk kmeans</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.5795779228210449</v>
+          <t>BoW kmeans</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>0.5337265071952092</v>
+        <v>0.127990835889721</v>
       </c>
       <c r="E26" t="n">
-        <v>107.7320098179871</v>
+        <v>2.309247279086911</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3074890077114105</v>
+        <v>7.970453853183063</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8448275862068966</v>
+        <v>174.9444444444445</v>
       </c>
     </row>
     <row r="27">
@@ -1096,23 +1146,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BoW kmeans</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.127990835889721</v>
+          <t>BoW affinity</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>2.309247279086911</v>
+        <v>0.1653661708272804</v>
       </c>
       <c r="E27" t="n">
-        <v>7.970453853183063</v>
+        <v>1.376051127811794</v>
       </c>
       <c r="F27" t="n">
-        <v>174.9444444444445</v>
+        <v>4.546676753605704</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7903225806451613</v>
+        <v>87.00555555555556</v>
       </c>
     </row>
     <row r="28">
@@ -1121,23 +1173,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DeepWalk affinity</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5820707678794861</v>
+          <t>BoW gmm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D28" t="n">
-        <v>0.4743835268905535</v>
+        <v>0.06176307381737975</v>
       </c>
       <c r="E28" t="n">
-        <v>271.9272229571449</v>
+        <v>3.333905797480221</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03935771156102419</v>
+        <v>4.052843509899693</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7000000000000001</v>
+        <v>188.3690476190476</v>
       </c>
     </row>
     <row r="29">
@@ -1146,23 +1200,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BoW affinity</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.1653661708272804</v>
+          <t>BoW agglomerative</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D29" t="n">
-        <v>1.376051127811794</v>
+        <v>0.120920844451319</v>
       </c>
       <c r="E29" t="n">
-        <v>4.546676753605704</v>
+        <v>2.395360391709118</v>
       </c>
       <c r="F29" t="n">
-        <v>87.00555555555556</v>
+        <v>7.423536863021071</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4537037037037037</v>
+        <v>176.7025089605735</v>
       </c>
     </row>
     <row r="30">
@@ -1171,23 +1227,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DeepWalk gmm</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.5374674797058105</v>
+          <t>DeepWalk kmeans</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5032301429420687</v>
+        <v>0.5601266622543335</v>
       </c>
       <c r="E30" t="n">
-        <v>73.94951140589549</v>
+        <v>0.5995029744873289</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3933739773929119</v>
+        <v>79.74916508397752</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7205882352941176</v>
+        <v>0.2477031797170639</v>
       </c>
     </row>
     <row r="31">
@@ -1196,23 +1254,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BoW gmm</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.06176307381737975</v>
+          <t>DeepWalk affinity</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>3.333905797480221</v>
+        <v>0.6753206849098206</v>
       </c>
       <c r="E31" t="n">
-        <v>4.052843509899693</v>
+        <v>0.3029285473897668</v>
       </c>
       <c r="F31" t="n">
-        <v>188.3690476190476</v>
+        <v>420.1901629963576</v>
       </c>
       <c r="G31" t="n">
-        <v>0.875</v>
+        <v>0.01094600857845762</v>
       </c>
     </row>
     <row r="32">
@@ -1221,23 +1281,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DeepWalk agglomerative</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.5822620987892151</v>
+          <t>DeepWalk gmm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D32" t="n">
-        <v>0.4345522143889293</v>
+        <v>0.4753953516483307</v>
       </c>
       <c r="E32" t="n">
-        <v>84.6856744145427</v>
+        <v>0.4942224331941519</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3613027650862932</v>
+        <v>32.56694872468799</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7</v>
+        <v>0.3945881938561797</v>
       </c>
     </row>
     <row r="33">
@@ -1246,23 +1308,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BoW agglomerative</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.120920844451319</v>
+          <t>DeepWalk agglomerative</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D33" t="n">
-        <v>2.395360391709118</v>
+        <v>0.5540092587471008</v>
       </c>
       <c r="E33" t="n">
-        <v>7.423536863021071</v>
+        <v>0.6284090697744877</v>
       </c>
       <c r="F33" t="n">
-        <v>176.7025089605735</v>
+        <v>76.80361397871279</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.2535965591669083</v>
       </c>
     </row>
     <row r="34">
@@ -1271,23 +1335,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DeepWalk kmeans</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.5529454350471497</v>
+          <t>BoW kmeans</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>0.5975655734933437</v>
+        <v>0.1164724725352648</v>
       </c>
       <c r="E34" t="n">
-        <v>92.72463649091726</v>
+        <v>2.505825156932492</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3539916053414345</v>
+        <v>7.290205696080375</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8387096774193549</v>
+        <v>186.81875</v>
       </c>
     </row>
     <row r="35">
@@ -1296,23 +1362,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BoW kmeans</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.1164724725352648</v>
+          <t>BoW affinity</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>2.505825156932492</v>
+        <v>0.1596419563771262</v>
       </c>
       <c r="E35" t="n">
-        <v>7.290205696080375</v>
+        <v>1.316939721822016</v>
       </c>
       <c r="F35" t="n">
-        <v>186.81875</v>
+        <v>4.611977834150649</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8125</v>
+        <v>100.7390692640693</v>
       </c>
     </row>
     <row r="36">
@@ -1321,23 +1389,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DeepWalk affinity</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.5564517378807068</v>
+          <t>BoW gmm</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D36" t="n">
-        <v>0.4396162978236164</v>
+        <v>0.1027070860266073</v>
       </c>
       <c r="E36" t="n">
-        <v>240.1669388901101</v>
+        <v>2.701386052874069</v>
       </c>
       <c r="F36" t="n">
-        <v>0.04713053605519235</v>
+        <v>6.617497456765004</v>
       </c>
       <c r="G36" t="n">
-        <v>0.65</v>
+        <v>189.0384615384615</v>
       </c>
     </row>
     <row r="37">
@@ -1346,23 +1416,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BoW affinity</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.1596419563771262</v>
+          <t>BoW agglomerative</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D37" t="n">
-        <v>1.316939721822016</v>
+        <v>0.1151247413131165</v>
       </c>
       <c r="E37" t="n">
-        <v>4.611977834150649</v>
+        <v>2.48766442875122</v>
       </c>
       <c r="F37" t="n">
-        <v>100.7390692640693</v>
+        <v>7.149378779858921</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4297520661157025</v>
+        <v>187.2791068580542</v>
       </c>
     </row>
     <row r="38">
@@ -1371,23 +1443,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DeepWalk gmm</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.5041029453277588</v>
+          <t>DeepWalk kmeans</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D38" t="n">
-        <v>0.3942874911438798</v>
+        <v>0.6120653748512268</v>
       </c>
       <c r="E38" t="n">
-        <v>42.08559510144168</v>
+        <v>0.5298505494860984</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5486559877172112</v>
+        <v>126.99692847176</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.2442198544740677</v>
       </c>
     </row>
     <row r="39">
@@ -1396,23 +1470,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BoW gmm</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.1027070860266073</v>
+          <t>DeepWalk affinity</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D39" t="n">
-        <v>2.701386052874069</v>
+        <v>0.5842556357383728</v>
       </c>
       <c r="E39" t="n">
-        <v>6.617497456765004</v>
+        <v>0.4778419755456437</v>
       </c>
       <c r="F39" t="n">
-        <v>189.0384615384615</v>
+        <v>228.3527605773435</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.0423074783757329</v>
       </c>
     </row>
     <row r="40">
@@ -1421,23 +1497,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DeepWalk agglomerative</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.4684440493583679</v>
+          <t>DeepWalk gmm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D40" t="n">
-        <v>0.6924703514653026</v>
+        <v>0.6007407903671265</v>
       </c>
       <c r="E40" t="n">
-        <v>69.35074124117308</v>
+        <v>0.526183512283143</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4233181327581406</v>
+        <v>122.6624519429807</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.2503506168723106</v>
       </c>
     </row>
     <row r="41">
@@ -1446,23 +1524,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BoW agglomerative</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.1151247413131165</v>
+          <t>DeepWalk agglomerative</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D41" t="n">
-        <v>2.48766442875122</v>
+        <v>0.6120653748512268</v>
       </c>
       <c r="E41" t="n">
-        <v>7.149378779858921</v>
+        <v>0.5298505494860984</v>
       </c>
       <c r="F41" t="n">
-        <v>187.2791068580542</v>
+        <v>126.99692847176</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.2442198544740677</v>
       </c>
     </row>
     <row r="42">
@@ -1471,23 +1551,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DeepWalk kmeans</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.5978119969367981</v>
+          <t>BoW kmeans</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D42" t="n">
-        <v>0.5071621597464145</v>
+        <v>0.2024554776850852</v>
       </c>
       <c r="E42" t="n">
-        <v>127.4656314025455</v>
+        <v>1.652594604121197</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3307098969817162</v>
+        <v>18.57969408837628</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7444444444444445</v>
+        <v>228.4583333333333</v>
       </c>
     </row>
     <row r="43">
@@ -1496,23 +1578,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BoW kmeans</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0.2024554776850852</v>
+          <t>BoW affinity</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D43" t="n">
-        <v>1.652594604121197</v>
+        <v>0.2335750628140043</v>
       </c>
       <c r="E43" t="n">
-        <v>18.57969408837628</v>
+        <v>1.427752700824287</v>
       </c>
       <c r="F43" t="n">
-        <v>228.4583333333333</v>
+        <v>9.208903887078286</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7790697674418605</v>
+        <v>103.3722222222222</v>
       </c>
     </row>
     <row r="44">
@@ -1521,23 +1605,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DeepWalk affinity</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0.5337479710578918</v>
+          <t>BoW gmm</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D44" t="n">
-        <v>0.5435487215348359</v>
+        <v>0.2016149474905295</v>
       </c>
       <c r="E44" t="n">
-        <v>312.3423810977278</v>
+        <v>1.621453081386175</v>
       </c>
       <c r="F44" t="n">
-        <v>0.03681081510148942</v>
+        <v>18.53808159126551</v>
       </c>
       <c r="G44" t="n">
-        <v>0.587719298245614</v>
+        <v>228.5721343873518</v>
       </c>
     </row>
     <row r="45">
@@ -1546,23 +1632,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BoW affinity</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0.2335750628140043</v>
+          <t>BoW agglomerative</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BoW</t>
+        </is>
       </c>
       <c r="D45" t="n">
-        <v>1.427752700824287</v>
+        <v>0.193956121844557</v>
       </c>
       <c r="E45" t="n">
-        <v>9.208903887078286</v>
+        <v>1.730463893026765</v>
       </c>
       <c r="F45" t="n">
-        <v>103.3722222222222</v>
+        <v>17.57972655975762</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5583333333333333</v>
+        <v>231.2247619047619</v>
       </c>
     </row>
     <row r="46">
@@ -1571,23 +1659,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DeepWalk gmm</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.5620043873786926</v>
+          <t>DeepWalk kmeans</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D46" t="n">
-        <v>0.467308942095516</v>
+        <v>0.5969101786613464</v>
       </c>
       <c r="E46" t="n">
-        <v>92.53176892970463</v>
+        <v>0.5157862164031713</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4040472954511642</v>
+        <v>121.557660670731</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6568627450980392</v>
+        <v>0.5694946423172951</v>
       </c>
     </row>
     <row r="47">
@@ -1596,23 +1686,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BoW gmm</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.2016149474905295</v>
+          <t>DeepWalk affinity</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D47" t="n">
-        <v>1.621453081386175</v>
+        <v>0.5627356171607971</v>
       </c>
       <c r="E47" t="n">
-        <v>18.53808159126551</v>
+        <v>0.4798295022221747</v>
       </c>
       <c r="F47" t="n">
-        <v>228.5721343873518</v>
+        <v>330.2594206009764</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7613636363636364</v>
+        <v>0.0480373646132648</v>
       </c>
     </row>
     <row r="48">
@@ -1621,23 +1713,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DeepWalk agglomerative</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.6112371683120728</v>
+          <t>DeepWalk gmm</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D48" t="n">
-        <v>0.4721010508288787</v>
+        <v>0.5969101786613464</v>
       </c>
       <c r="E48" t="n">
-        <v>125.1812464674928</v>
+        <v>0.5157862164031713</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3346822485327721</v>
+        <v>121.557660670731</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.5694946423172951</v>
       </c>
     </row>
     <row r="49">
@@ -1646,23 +1740,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BoW agglomerative</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.193956121844557</v>
+          <t>DeepWalk agglomerative</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DeepWalk</t>
+        </is>
       </c>
       <c r="D49" t="n">
-        <v>1.730463893026765</v>
+        <v>0.5969101786613464</v>
       </c>
       <c r="E49" t="n">
-        <v>17.57972655975762</v>
+        <v>0.5157862164031713</v>
       </c>
       <c r="F49" t="n">
-        <v>231.2247619047619</v>
+        <v>121.557660670731</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7976190476190477</v>
+        <v>0.5694946423172951</v>
       </c>
     </row>
   </sheetData>
